--- a/nr-update-patient-name/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-patient-name/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6870" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="847">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T13:41:02+00:00</t>
+    <t>2025-02-17T10:02:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1236,10 +1236,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1564,6 +1561,12 @@
     &lt;code value="INS-NIR"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.system</t>
@@ -3034,7 +3037,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.0703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>
@@ -8609,29 +8612,27 @@
       <c r="X48" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Y48" s="2"/>
+      <c r="Z48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8655,7 +8656,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8663,10 +8664,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8692,16 +8693,16 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8711,46 +8712,46 @@
         <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="T49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="T49" t="s" s="2">
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8765,16 +8766,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8782,10 +8783,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8811,13 +8812,13 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8831,43 +8832,43 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8882,16 +8883,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8899,10 +8900,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8928,10 +8929,10 @@
         <v>340</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8982,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8997,16 +8998,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -9014,10 +9015,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9040,16 +9041,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9099,7 +9100,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9114,16 +9115,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -9131,13 +9132,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -9162,7 +9163,7 @@
         <v>354</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>356</v>
@@ -9250,7 +9251,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>368</v>
@@ -9365,7 +9366,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>370</v>
@@ -9482,7 +9483,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>372</v>
@@ -9530,7 +9531,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9601,7 +9602,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>383</v>
@@ -9649,7 +9650,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9666,29 +9667,27 @@
       <c r="X57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Y57" s="2"/>
+      <c r="Z57" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9712,7 +9711,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9719,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9749,16 +9748,16 @@
         <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9768,46 +9767,46 @@
         <v>82</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9822,16 +9821,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9839,10 +9838,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9868,13 +9867,13 @@
         <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9888,43 +9887,43 @@
         <v>82</v>
       </c>
       <c r="T59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9939,16 +9938,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9956,10 +9955,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9985,10 +9984,10 @@
         <v>340</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10039,7 +10038,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10054,16 +10053,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -10071,10 +10070,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10097,16 +10096,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10156,7 +10155,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10171,16 +10170,16 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -10188,13 +10187,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -10219,7 +10218,7 @@
         <v>354</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>356</v>
@@ -10307,7 +10306,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>368</v>
@@ -10422,7 +10421,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>370</v>
@@ -10539,7 +10538,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>372</v>
@@ -10587,7 +10586,7 @@
         <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>82</v>
@@ -10658,7 +10657,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>383</v>
@@ -10706,7 +10705,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10723,29 +10722,27 @@
       <c r="X66" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Y66" s="2"/>
+      <c r="Z66" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10769,7 +10766,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10777,10 +10774,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10806,16 +10803,16 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10825,46 +10822,46 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T67" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10879,16 +10876,16 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10896,10 +10893,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10925,13 +10922,13 @@
         <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10945,43 +10942,43 @@
         <v>82</v>
       </c>
       <c r="T68" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10996,16 +10993,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -11013,10 +11010,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11042,10 +11039,10 @@
         <v>340</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11096,7 +11093,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11111,16 +11108,16 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -11128,10 +11125,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11154,16 +11151,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11213,7 +11210,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11228,16 +11225,16 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11245,13 +11242,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>82</v>
@@ -11276,7 +11273,7 @@
         <v>354</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>356</v>
@@ -11364,7 +11361,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>368</v>
@@ -11479,7 +11476,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>370</v>
@@ -11596,7 +11593,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>372</v>
@@ -11644,7 +11641,7 @@
         <v>82</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>82</v>
@@ -11715,7 +11712,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>383</v>
@@ -11763,7 +11760,7 @@
         <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>82</v>
@@ -11780,29 +11777,27 @@
       <c r="X75" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11826,7 +11821,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11834,10 +11829,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11863,16 +11858,16 @@
         <v>132</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11885,43 +11880,43 @@
         <v>82</v>
       </c>
       <c r="T76" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11936,16 +11931,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11953,10 +11948,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11982,13 +11977,13 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12002,43 +11997,43 @@
         <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12053,16 +12048,16 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -12070,10 +12065,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12099,10 +12094,10 @@
         <v>340</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12153,7 +12148,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12168,16 +12163,16 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -12185,10 +12180,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12211,16 +12206,16 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12270,7 +12265,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12285,16 +12280,16 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12302,13 +12297,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>82</v>
@@ -12333,7 +12328,7 @@
         <v>354</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>356</v>
@@ -12421,7 +12416,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>368</v>
@@ -12536,7 +12531,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>370</v>
@@ -12653,7 +12648,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>372</v>
@@ -12701,7 +12696,7 @@
         <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>82</v>
@@ -12772,7 +12767,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>383</v>
@@ -12820,7 +12815,7 @@
         <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>82</v>
@@ -12837,29 +12832,27 @@
       <c r="X84" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Y84" s="2"/>
+      <c r="Z84" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12883,7 +12876,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12891,10 +12884,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12920,16 +12913,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12942,43 +12935,43 @@
         <v>82</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12993,16 +12986,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -13010,10 +13003,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13039,13 +13032,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13059,43 +13052,43 @@
         <v>82</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13110,16 +13103,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -13127,10 +13120,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13156,10 +13149,10 @@
         <v>340</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13210,7 +13203,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13225,16 +13218,16 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13242,10 +13235,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13268,16 +13261,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13327,7 +13320,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13342,16 +13335,16 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13359,13 +13352,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>82</v>
@@ -13390,7 +13383,7 @@
         <v>354</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>356</v>
@@ -13478,7 +13471,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>368</v>
@@ -13593,7 +13586,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>370</v>
@@ -13710,7 +13703,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>372</v>
@@ -13829,7 +13822,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>383</v>
@@ -13877,7 +13870,7 @@
         <v>82</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>82</v>
@@ -13895,28 +13888,28 @@
         <v>154</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13940,7 +13933,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13948,10 +13941,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13977,16 +13970,16 @@
         <v>132</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13996,46 +13989,46 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="T94" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="T94" t="s" s="2">
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14050,16 +14043,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -14067,10 +14060,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14096,13 +14089,13 @@
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14116,43 +14109,43 @@
         <v>82</v>
       </c>
       <c r="T95" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14167,16 +14160,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14184,10 +14177,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14213,10 +14206,10 @@
         <v>340</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14267,7 +14260,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14282,16 +14275,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14299,10 +14292,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14325,16 +14318,16 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14384,7 +14377,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14399,16 +14392,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14416,13 +14409,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -14447,7 +14440,7 @@
         <v>354</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>356</v>
@@ -14535,7 +14528,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>368</v>
@@ -14650,7 +14643,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>370</v>
@@ -14767,7 +14760,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>372</v>
@@ -14886,7 +14879,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>383</v>
@@ -14934,7 +14927,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14952,28 +14945,28 @@
         <v>154</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z102" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14997,7 +14990,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -15005,10 +14998,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15034,16 +15027,16 @@
         <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15053,46 +15046,46 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15107,16 +15100,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15124,10 +15117,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15153,13 +15146,13 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15173,43 +15166,43 @@
         <v>82</v>
       </c>
       <c r="T104" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15224,16 +15217,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15241,10 +15234,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15270,10 +15263,10 @@
         <v>340</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15324,7 +15317,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15339,16 +15332,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15356,10 +15349,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15382,16 +15375,16 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15441,7 +15434,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15456,16 +15449,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15473,13 +15466,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -15504,7 +15497,7 @@
         <v>354</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M107" t="s" s="2">
         <v>356</v>
@@ -15592,7 +15585,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>368</v>
@@ -15707,7 +15700,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>370</v>
@@ -15824,7 +15817,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>372</v>
@@ -15943,7 +15936,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>383</v>
@@ -15991,7 +15984,7 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>82</v>
@@ -16009,28 +16002,28 @@
         <v>154</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z111" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16054,7 +16047,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16062,10 +16055,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16091,16 +16084,16 @@
         <v>132</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16110,46 +16103,46 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="T112" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16164,16 +16157,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16181,10 +16174,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16210,13 +16203,13 @@
         <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16230,43 +16223,43 @@
         <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16281,16 +16274,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16298,10 +16291,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16327,10 +16320,10 @@
         <v>340</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16381,7 +16374,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16396,16 +16389,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16413,10 +16406,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16439,16 +16432,16 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16498,7 +16491,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16513,16 +16506,16 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16530,13 +16523,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>82</v>
@@ -16561,7 +16554,7 @@
         <v>354</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>356</v>
@@ -16649,7 +16642,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>368</v>
@@ -16764,7 +16757,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>370</v>
@@ -16881,7 +16874,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>372</v>
@@ -16929,7 +16922,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>82</v>
@@ -17000,7 +16993,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>383</v>
@@ -17048,7 +17041,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17066,28 +17059,28 @@
         <v>154</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z120" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17111,7 +17104,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17119,10 +17112,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17148,16 +17141,16 @@
         <v>132</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -17167,46 +17160,46 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="T121" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17221,16 +17214,16 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17238,10 +17231,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17267,13 +17260,13 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17287,43 +17280,43 @@
         <v>82</v>
       </c>
       <c r="T122" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17338,16 +17331,16 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17355,10 +17348,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17384,10 +17377,10 @@
         <v>340</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17438,7 +17431,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17453,16 +17446,16 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17470,10 +17463,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17496,16 +17489,16 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17555,7 +17548,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17570,16 +17563,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17587,10 +17580,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17613,70 +17606,70 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q125" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="R125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17691,13 +17684,13 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17708,10 +17701,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17734,19 +17727,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17783,7 +17776,7 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
@@ -17793,7 +17786,7 @@
         <v>117</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17808,16 +17801,16 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17825,13 +17818,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>82</v>
@@ -17853,19 +17846,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17914,7 +17907,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17929,16 +17922,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17946,10 +17939,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18061,10 +18054,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18178,10 +18171,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18207,16 +18200,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18226,7 +18219,7 @@
         <v>82</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>82</v>
@@ -18244,10 +18237,10 @@
         <v>260</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -18265,7 +18258,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18289,7 +18282,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -18297,10 +18290,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18326,13 +18319,13 @@
         <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O131" t="s" s="2">
         <v>281</v>
@@ -18384,7 +18377,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18408,7 +18401,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18416,14 +18409,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18445,13 +18438,13 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18501,7 +18494,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18516,7 +18509,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18525,7 +18518,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18533,14 +18526,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18562,13 +18555,13 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18618,7 +18611,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18633,7 +18626,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18642,7 +18635,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18650,10 +18643,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18679,10 +18672,10 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18733,7 +18726,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18748,7 +18741,7 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18757,7 +18750,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18765,10 +18758,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18794,10 +18787,10 @@
         <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18848,7 +18841,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18863,7 +18856,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18872,7 +18865,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18880,10 +18873,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18909,14 +18902,14 @@
         <v>340</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18965,7 +18958,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18989,7 +18982,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18997,13 +18990,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>82</v>
@@ -19025,19 +19018,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19086,7 +19079,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19101,16 +19094,16 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19118,10 +19111,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19233,10 +19226,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19348,13 +19341,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>82</v>
@@ -19376,13 +19369,13 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19465,10 +19458,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19494,16 +19487,16 @@
         <v>172</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19531,10 +19524,10 @@
         <v>260</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19552,7 +19545,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19576,7 +19569,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19584,10 +19577,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19613,13 +19606,13 @@
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>281</v>
@@ -19671,7 +19664,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19695,7 +19688,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19703,14 +19696,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19732,13 +19725,13 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19788,7 +19781,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19803,7 +19796,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>82</v>
@@ -19812,7 +19805,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19820,14 +19813,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19849,13 +19842,13 @@
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19905,7 +19898,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19920,7 +19913,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>82</v>
@@ -19929,7 +19922,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19937,10 +19930,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19966,10 +19959,10 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20020,7 +20013,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20035,7 +20028,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20044,7 +20037,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20052,10 +20045,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20081,10 +20074,10 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20135,7 +20128,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20150,7 +20143,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20159,7 +20152,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20167,10 +20160,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20196,14 +20189,14 @@
         <v>340</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20252,7 +20245,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20276,7 +20269,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20284,10 +20277,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20310,19 +20303,19 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20371,7 +20364,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20386,16 +20379,16 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20403,10 +20396,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20432,16 +20425,16 @@
         <v>172</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20470,7 +20463,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20488,7 +20481,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20503,16 +20496,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20520,10 +20513,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20546,19 +20539,19 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20607,7 +20600,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20622,27 +20615,27 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20665,19 +20658,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20726,7 +20719,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20741,7 +20734,7 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>108</v>
@@ -20750,7 +20743,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20758,10 +20751,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20787,16 +20780,16 @@
         <v>239</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20845,7 +20838,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20860,16 +20853,16 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20877,10 +20870,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20906,14 +20899,14 @@
         <v>384</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20942,7 +20935,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -20960,7 +20953,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20975,16 +20968,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -20992,10 +20985,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21018,19 +21011,19 @@
         <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21079,7 +21072,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21094,7 +21087,7 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>108</v>
@@ -21103,7 +21096,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21111,10 +21104,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21137,19 +21130,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21198,7 +21191,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21213,7 +21206,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21222,7 +21215,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21230,10 +21223,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21256,19 +21249,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21317,7 +21310,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21329,10 +21322,10 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>108</v>
@@ -21349,10 +21342,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21464,10 +21457,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21577,13 +21570,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="B159" t="s" s="2">
-        <v>718</v>
-      </c>
       <c r="C159" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>82</v>
@@ -21605,13 +21598,13 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21694,13 +21687,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -21722,13 +21715,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21811,14 +21804,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -21840,10 +21833,10 @@
         <v>111</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>114</v>
@@ -21898,7 +21891,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21930,10 +21923,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21959,14 +21952,14 @@
         <v>384</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21994,16 +21987,16 @@
         <v>154</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
@@ -22013,7 +22006,7 @@
         <v>117</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22028,7 +22021,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>108</v>
@@ -22037,7 +22030,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22045,13 +22038,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>82</v>
@@ -22076,14 +22069,14 @@
         <v>384</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22112,7 +22105,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22130,7 +22123,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22145,7 +22138,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22154,7 +22147,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22162,13 +22155,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22193,14 +22186,14 @@
         <v>384</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22229,7 +22222,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22247,7 +22240,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22262,7 +22255,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22271,7 +22264,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22279,10 +22272,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22305,17 +22298,17 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22364,7 +22357,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22379,7 +22372,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>108</v>
@@ -22388,7 +22381,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22396,10 +22389,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22422,19 +22415,19 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22483,7 +22476,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22498,7 +22491,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22507,7 +22500,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22515,10 +22508,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22541,17 +22534,17 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22600,7 +22593,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22615,7 +22608,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>108</v>
@@ -22624,7 +22617,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22632,10 +22625,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22661,14 +22654,14 @@
         <v>172</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22696,10 +22689,10 @@
         <v>260</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22717,7 +22710,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22732,7 +22725,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22741,7 +22734,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22749,10 +22742,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22775,17 +22768,17 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22834,7 +22827,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22843,13 +22836,13 @@
         <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22858,7 +22851,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22866,10 +22859,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22895,10 +22888,10 @@
         <v>340</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22949,7 +22942,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22964,7 +22957,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22981,10 +22974,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23007,19 +23000,19 @@
         <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -23068,7 +23061,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23083,10 +23076,10 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>82</v>
@@ -23100,10 +23093,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23215,10 +23208,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23332,14 +23325,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -23361,10 +23354,10 @@
         <v>111</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>114</v>
@@ -23419,7 +23412,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23451,10 +23444,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23480,16 +23473,16 @@
         <v>384</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23538,7 +23531,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>90</v>
@@ -23553,16 +23546,16 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -23570,10 +23563,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23596,19 +23589,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23657,7 +23650,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23672,16 +23665,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23689,14 +23682,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23715,16 +23708,16 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23774,7 +23767,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23789,7 +23782,7 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>108</v>
@@ -23798,7 +23791,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23806,10 +23799,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23832,19 +23825,19 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23893,7 +23886,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23908,10 +23901,10 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>82</v>
@@ -23925,10 +23918,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23951,19 +23944,19 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24012,7 +24005,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24027,7 +24020,7 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>108</v>
@@ -24044,10 +24037,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24159,10 +24152,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24276,14 +24269,14 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -24305,10 +24298,10 @@
         <v>111</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N182" t="s" s="2">
         <v>114</v>
@@ -24363,7 +24356,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24395,10 +24388,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24421,16 +24414,16 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24480,7 +24473,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>90</v>
@@ -24504,7 +24497,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24512,10 +24505,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24541,10 +24534,10 @@
         <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24574,10 +24567,10 @@
         <v>260</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -24595,7 +24588,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24610,7 +24603,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>108</v>
